--- a/output/2026-09-17_MACD柱狀圖動能量化_轉勢指標.xlsx
+++ b/output/2026-09-17_MACD柱狀圖動能量化_轉勢指標.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_四色柱示意圖" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_實戰應用與陷阱" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_如何換入真實資料" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV_連結" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -919,6 +920,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -933,6 +935,7 @@
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -1125,6 +1128,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -1277,6 +1281,7 @@
         <v>1.707</v>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -1341,6 +1346,66 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>TradingView 連結索引（本檔案出現過的所有代號）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>原地已加連結的儲存格：0 個。另有 0 個儲存格同時提及多個代號 —— Excel 不支援在單一儲存格內為部分文字加連結，故該類儲存格不在原地處理，改由本表覆蓋。點擊下方連結即可開啟該代號的 TradingView 圖表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>出現位置</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1504,6 +1569,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
@@ -1586,6 +1652,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
@@ -1989,6 +2056,8 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -3084,6 +3153,7 @@
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="4" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -3156,6 +3226,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -3717,6 +3788,7 @@
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -3802,6 +3874,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="75" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
@@ -3977,6 +4050,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -4085,6 +4159,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5128,6 +5203,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
